--- a/artfynd/A 32782-2022 artfynd.xlsx
+++ b/artfynd/A 32782-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32782-2022 artfynd.xlsx
+++ b/artfynd/A 32782-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4171499</v>
+        <v>5046855</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
+        <v>98519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495675.40271263</v>
+        <v>495646.221521138</v>
       </c>
       <c r="R2" t="n">
-        <v>6572734.202022329</v>
+        <v>6572721.97599093</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5046855</v>
+        <v>4815303</v>
       </c>
       <c r="B3" t="n">
-        <v>98519</v>
+        <v>97050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,43 +812,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limberget O-ut, Nrk</t>
+          <t>Kalkberget-Kanterboda, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495646.221521138</v>
+        <v>495756.2411022181</v>
       </c>
       <c r="R3" t="n">
-        <v>6572721.97599093</v>
+        <v>6572724.405440295</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +870,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-05-20</t>
+          <t>2010-09-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -885,7 +880,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-05-20</t>
+          <t>2010-10-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -902,14 +897,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -918,122 +905,10 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4815303</v>
-      </c>
-      <c r="B4" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222361</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Loppstarr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kalkberget-Kanterboda, Nrk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>495756.2411022181</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6572724.405440295</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Vintrosa</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2010-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Tommy Pettersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>

--- a/artfynd/A 32782-2022 artfynd.xlsx
+++ b/artfynd/A 32782-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5046855</v>
+        <v>4171499</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
+        <v>95510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495646.221521138</v>
+        <v>495675.40271263</v>
       </c>
       <c r="R2" t="n">
-        <v>6572721.97599093</v>
+        <v>6572734.202022329</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4815303</v>
+        <v>5046855</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
+        <v>98519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,38 +812,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkberget-Kanterboda, Nrk</t>
+          <t>Limberget O-ut, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495756.2411022181</v>
+        <v>495646.221521138</v>
       </c>
       <c r="R3" t="n">
-        <v>6572724.405440295</v>
+        <v>6572721.97599093</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +875,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-01</t>
+          <t>2009-05-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -880,7 +885,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-10-31</t>
+          <t>2009-05-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -897,6 +902,14 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -905,10 +918,122 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4815303</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97050</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalkberget-Kanterboda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>495756.2411022181</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572724.405440295</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-10-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Tommy Pettersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>

--- a/artfynd/A 32782-2022 artfynd.xlsx
+++ b/artfynd/A 32782-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4171499</v>
+        <v>55235457</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>4368</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Limberget O-ut, Nrk</t>
+          <t>Kanterboda NR, i söder, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495675.40271263</v>
+        <v>495640</v>
       </c>
       <c r="R2" t="n">
-        <v>6572734.202022329</v>
+        <v>6572729</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca 35 fräscha och 25 gamla fruktkroppar i en drygt 5 m stor häxring</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,41 +769,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Granskog på kalk</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5046855</v>
+        <v>55207916</v>
       </c>
       <c r="B3" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,42 +804,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limberget O-ut, Nrk</t>
+          <t>Lannafors, Kanterboda, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495646.221521138</v>
+        <v>495794</v>
       </c>
       <c r="R3" t="n">
-        <v>6572721.97599093</v>
+        <v>6572722</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-05-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,76 +889,82 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kärr, öppet</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4815303</v>
+        <v>55207918</v>
       </c>
       <c r="B4" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222361</v>
+        <v>219788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalkberget-Kanterboda, Nrk</t>
+          <t>Lannafors, Kanterboda, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495756.2411022181</v>
+        <v>495803</v>
       </c>
       <c r="R4" t="n">
-        <v>6572724.405440295</v>
+        <v>6572722</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,22 +988,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,23 +1004,683 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kärr, öppet</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4171499</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Limberget O-ut, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495675</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6572734</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-05-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-05-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Henrik Josefsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102341213</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lannaforskärret, Kanterboda naturreservat, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495773</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572795</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4815303</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalkberget-Kanterboda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495756</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6572724</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2010-10-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Tommy Pettersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>58821330</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Limberget, OSO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495746</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6572531</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-04-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-04-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blandskog, fuktig, kalkrik, vid dike</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>58821335</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Limberget, OSO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495746</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6572542</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-04-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-04-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskog, fuktig, kalkrik</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5046855</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Limberget O-ut, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>495646</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6572722</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2009-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2009-05-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32782-2022 artfynd.xlsx
+++ b/artfynd/A 32782-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55235457</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55207916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55207918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4171499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102341213</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4815303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58821330</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1571,6 +1611,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58821335</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,8 +1726,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5046855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>